--- a/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10.18%11,864,000</t>
+          <t>10.42%11,864,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.18%</t>
+          <t>10.42%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.15%4,750,000</t>
+          <t>8.95%4,750,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.15%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.53%5,186,000</t>
+          <t>8.46%5,186,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.46%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3310</v>
+        <v>951</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.10%5,949,000</t>
+          <t>7.11%20,300,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>7.11%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5949000</v>
+        <v>20300000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>970</v>
+        <v>3115</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.10%20,300,000</t>
+          <t>6.82%5,949,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>6.82%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>20300000</v>
+        <v>5949000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.42%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.31%6,490,561</t>
+          <t>5.53%6,490,561</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.31%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5820</v>
+        <v>5440</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.27%2,512,000</t>
+          <t>5.10%2,546,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>5.10%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2512000</v>
+        <v>2546000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5620</v>
+        <v>537</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.14%2,546,000</t>
+          <t>4.94%24,987,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2546000</v>
+        <v>24987000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,25 +992,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>545</v>
+        <v>5310</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.91%24,987,000</t>
+          <t>4.91%2,512,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24987000</v>
+        <v>2512000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.42%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>142.5</v>
+        <v>138.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.58%89,118,000</t>
+          <t>4.54%89,118,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1875</v>
+        <v>1670</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.37%6,464,000</t>
+          <t>4.45%7,240,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.37%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6464000</v>
+        <v>7240000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1620</v>
+        <v>1840</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.23%7,240,000</t>
+          <t>4.38%6,464,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7240000</v>
+        <v>6464000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.97%612</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+2.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>612</v>
+        <v>1085</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.71%16,811,000</t>
+          <t>3.77%9,426,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16811000</v>
+        <v>9426000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>-3.27%592</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1055</v>
+        <v>592</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.59%9,426,000</t>
+          <t>3.66%16,811,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>9426000</v>
+        <v>16811000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:19</t>
+          <t>2026-09-15 19:50:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.27%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1955</v>
+        <v>1980</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.02%4,280,848</t>
+          <t>3.12%4,280,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.74%5,398,000</t>
+          <t>2.72%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,40 +1482,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.35%1,731,000</t>
+          <t>1.34%207,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1731000</v>
+        <v>207900</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,40 +1545,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-6.47%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.35%207,900</t>
+          <t>1.29%1,731,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>207900</v>
+        <v>1731000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>261.5</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.95%413,000</t>
+          <t>0.92%413,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,27 +1739,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-5.18%3480</t>
+          <t>-3.56%3255</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3255</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.54%446,000</t>
+          <t>0.53%446,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,36 +1797,36 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>8210勤誠</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-1.35%874</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>489.5</t>
+          <t>874</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.48%2,712,000</t>
+          <t>0.49%1,516,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2712000</v>
+        <v>1516000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,27 +1860,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8210勤誠</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.56%886</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>477.5</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.48%1,516,000</t>
+          <t>0.48%2,712,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1516000</v>
+        <v>2712000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,17 +1928,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>-2.86%221</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-2.86%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>230.5</t>
+          <t>221</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,36 +1986,36 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-2.7%180.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.21%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>180.5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.23%95,000</t>
+          <t>0.22%3,248,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>95000</v>
+        <v>3248000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-0.54%185.5</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>185.5</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.22%3,248,000</t>
+          <t>0.22%485,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2078,7 +2078,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3248000</v>
+        <v>485000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,27 +2112,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-4.39%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.22%485,000</t>
+          <t>0.22%95,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2141,11 +2141,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>485000</v>
+        <v>95000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0%220</t>
+          <t>+0.45%221</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:20</t>
+          <t>2026-09-15 19:50:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,17 +2243,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.36%82</t>
+          <t>-1.22%81</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.09%181</t>
+          <t>-4.42%173</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2367,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>-4.71%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1020</v>
+        <v>972</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,25 +2423,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.23%221</t>
+          <t>-0.8%18.65</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>221</v>
+        <v>18.65</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0.04%5,163,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>501000</v>
+        <v>5163000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.53%18.8</t>
+          <t>-1.13%218.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>18.8</v>
+        <v>218.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>5163000</v>
+        <v>501000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-6.91%485</t>
+          <t>-6.95%482</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.64%3590</t>
+          <t>-6.55%3355</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>-6.55%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3590</v>
+        <v>3355</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.05%77.3</t>
+          <t>-0.91%76.6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>77.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.17%1270</t>
+          <t>+0.79%1280</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.17%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1270</v>
+        <v>1280</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.98%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5995</v>
+        <v>6055</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.19%332.5</t>
+          <t>+0.15%333</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>332.5</v>
+        <v>333</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.34%1250</t>
+          <t>-0.82%1215</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.34%</t>
+          <t>-0.82%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1250</v>
+        <v>1215</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-7.01%531</t>
+          <t>-6.95%509</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-7.01%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.59%465.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%101</t>
+          <t>-4.06%96.9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.06%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>101</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:21</t>
+          <t>2026-09-15 19:51:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.93%2140</t>
+          <t>-2.8%2080</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2140</v>
+        <v>2080</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.64%902</t>
+          <t>+1.56%914</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.56%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.22%528</t>
+          <t>-2.61%523</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.12%86.6</t>
+          <t>-2.54%84.4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>86.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.2%248.5</t>
+          <t>-0.8%246.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>248.5</v>
+        <v>246.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.48%157.5</t>
+          <t>-4.08%153</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-4.08%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>157.5</v>
+        <v>153</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:01:23</t>
+          <t>2026-09-15 19:51:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+6%159</t>
+          <t>-3.46%153.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+6%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>159</v>
+        <v>153.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:45</t>
+          <t>2026-09-15 21:11:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 19:50:56</t>
+          <t>2026-09-15 21:11:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:07</t>
+          <t>2026-09-15 21:11:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 19:51:19</t>
+          <t>2026-09-15 21:11:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:35</t>
+          <t>2026-09-15 22:21:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:37</t>
+          <t>2026-09-15 22:21:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:38</t>
+          <t>2026-09-15 22:21:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:11:39</t>
+          <t>2026-09-15 22:21:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:51</t>
+          <t>2026-09-15 22:27:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:56</t>
+          <t>2026-09-15 22:27:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:58</t>
+          <t>2026-09-15 22:27:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:21:59</t>
+          <t>2026-09-15 22:27:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
